--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/XRF/Panel 02/front/xrf_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/XRF/Panel 02/front/xrf_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.21298</v>
+        <v>17.07772</v>
       </c>
       <c r="D2" t="n">
-        <v>16.98035</v>
+        <v>16.61544</v>
       </c>
       <c r="E2" t="n">
-        <v>16.87796</v>
+        <v>16.97496</v>
       </c>
       <c r="F2" t="n">
-        <v>43.40308</v>
+        <v>42.92562</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05092</v>
+        <v>0.05205</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81415</v>
+        <v>1.87383</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.08106</v>
+        <v>17.16836</v>
       </c>
       <c r="D3" t="n">
-        <v>16.85548</v>
+        <v>16.50275</v>
       </c>
       <c r="E3" t="n">
-        <v>16.65292</v>
+        <v>16.75672</v>
       </c>
       <c r="F3" t="n">
-        <v>43.35459</v>
+        <v>43.2422</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05085</v>
+        <v>0.05196</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84183</v>
+        <v>1.81731</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.68612</v>
+        <v>17.14413</v>
       </c>
       <c r="D4" t="n">
-        <v>16.07006</v>
+        <v>16.68418</v>
       </c>
       <c r="E4" t="n">
-        <v>16.92865</v>
+        <v>16.85579</v>
       </c>
       <c r="F4" t="n">
-        <v>42.71627</v>
+        <v>42.8786</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05088</v>
+        <v>0.05228</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83962</v>
+        <v>1.83284</v>
       </c>
     </row>
   </sheetData>
